--- a/output/pdf_financials_xlsx/AWX.xlsx
+++ b/output/pdf_financials_xlsx/AWX.xlsx
@@ -5056,43 +5056,43 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.077846</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.090998</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.090998</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.090998</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.090998</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.120642</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.527737</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.023413</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.277274</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.289869</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.366219</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.478185</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.482909</v>
       </c>
     </row>
     <row r="93">
@@ -8234,7 +8234,11 @@
           <t>Share-based payment reserve 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -8794,7 +8798,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -10008,7 +10016,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -11024,7 +11036,11 @@
           <t>Share based payments Reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -11456,7 +11472,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -11706,7 +11726,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -12386,7 +12410,11 @@
           <t>Reserves (Note 4)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AWX.xlsx
+++ b/output/pdf_financials_xlsx/AWX.xlsx
@@ -939,46 +939,46 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000308</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.006713</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.006986</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.005335</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.004988</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.002315</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002209</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.014372</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.021629</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.008744</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.017556</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.053732</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.078398</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.07981000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1748,46 +1748,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.01394</v>
+        <v>-0.014248</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.09003800000000001</v>
+        <v>-0.096751</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.141434</v>
+        <v>-0.14842</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.071412</v>
+        <v>-0.076747</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.148934</v>
+        <v>-0.153922</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.321614</v>
+        <v>-0.323929</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.390421</v>
+        <v>-0.39263</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.805389</v>
+        <v>-0.819761</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.146505</v>
+        <v>-1.168134</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.355947</v>
+        <v>-0.364691</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.79753</v>
+        <v>-0.815086</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.342137</v>
+        <v>-0.395869</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.449816</v>
+        <v>-0.528214</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.154226</v>
+        <v>0.074416</v>
       </c>
     </row>
     <row r="28">
@@ -1846,46 +1846,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.01394</v>
+        <v>-0.014248</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.09003800000000001</v>
+        <v>-0.096751</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.141434</v>
+        <v>-0.14842</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.071412</v>
+        <v>-0.076747</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.148934</v>
+        <v>-0.153922</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.321614</v>
+        <v>-0.323929</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.390421</v>
+        <v>-0.39263</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.8053630000000001</v>
+        <v>-0.819735</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.145739</v>
+        <v>-1.167368</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.350119</v>
+        <v>-0.358863</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.778164</v>
+        <v>-0.79572</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.322091</v>
+        <v>-0.375823</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.434792</v>
+        <v>-0.51319</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.155515</v>
+        <v>0.07570499999999999</v>
       </c>
     </row>
     <row r="30">
@@ -9228,7 +9228,11 @@
           <t>Reclamation deposit 7</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -16772,7 +16776,11 @@
           <t>Reclamation Deposit</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -24220,7 +24228,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -28280,7 +28288,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -28886,7 +28894,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E258" s="5" t="n">

--- a/output/pdf_financials_xlsx/AWX.xlsx
+++ b/output/pdf_financials_xlsx/AWX.xlsx
@@ -724,16 +724,16 @@
         <v>0.012759</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.055438</v>
+        <v>0.085438</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.060562</v>
+        <v>0.081095</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.010098</v>
+        <v>0.027594</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.003682</v>
+        <v>0.019217</v>
       </c>
     </row>
     <row r="8">
@@ -871,16 +871,16 @@
         <v>0.039248</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.07729900000000001</v>
+        <v>0.107299</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.08300100000000001</v>
+        <v>0.103534</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.035003</v>
+        <v>0.052499</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.024</v>
+        <v>0.039535</v>
       </c>
     </row>
     <row r="11">
@@ -3625,28 +3625,28 @@
         <v>0.043561</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.036363</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.045852</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.078221</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.034379</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>0.025655</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.022073</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.023139</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>0.078026</v>
       </c>
     </row>
     <row r="65">
@@ -3772,28 +3772,28 @@
         <v>0.01</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.012</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.018235</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.0355</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.0265</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.067645</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.059165</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.039668</v>
       </c>
     </row>
     <row r="68">
@@ -5965,16 +5965,16 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.001904</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.055635</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003665</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002442</v>
       </c>
     </row>
     <row r="112">
@@ -6164,22 +6164,22 @@
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.194978</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.362806</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.020745</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.180745</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.573569</v>
       </c>
     </row>
     <row r="116">
@@ -7168,16 +7168,16 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.001904</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.055635</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003665</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002442</v>
       </c>
     </row>
     <row r="135">
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="O135" s="3" t="n">
-        <v>0.604673</v>
+        <v>0.602231</v>
       </c>
     </row>
   </sheetData>
@@ -13468,7 +13468,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -13546,7 +13550,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -15922,7 +15930,11 @@
           <t>Proceeds from sale of marketable securities 5</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -17380,7 +17392,11 @@
           <t>Issuance of shares pursuant to private placement</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -22234,7 +22250,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E179" s="5" t="n">
         <v>0.6036</v>
       </c>
@@ -23516,7 +23536,11 @@
           <t>Director fees 10</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -25376,7 +25400,11 @@
           <t>Director fees 11</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
